--- a/Data/VaccineSchedule.xlsx
+++ b/Data/VaccineSchedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2025/18 百日咳疫苗/code/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2025/28 百日咳数据对比/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="682" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB7DBAC-A00E-4F48-AD3E-A188FDB63A70}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C95ABF70-0610-4061-B0C0-FE8E490CE03B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
+    <workbookView xWindow="9280" yWindow="2090" windowWidth="28800" windowHeight="15460" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
   </bookViews>
   <sheets>
     <sheet name="VaccineSchedule" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="477">
   <si>
     <t>CODE</t>
   </si>
@@ -139,10 +139,6 @@
     <t>Argentina</t>
   </si>
   <si>
-    <t>20-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8876368/</t>
   </si>
   <si>
@@ -349,9 +345,6 @@
     <t>Chile</t>
   </si>
   <si>
-    <t>28w onwards</t>
-  </si>
-  <si>
     <t>CHN</t>
   </si>
   <si>
@@ -416,9 +409,6 @@
     <t>Costa Rica</t>
   </si>
   <si>
-    <t>3rd trim</t>
-  </si>
-  <si>
     <t>CUB</t>
   </si>
   <si>
@@ -456,10 +446,6 @@
     <t>Germany</t>
   </si>
   <si>
-    <t>28-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DJI</t>
   </si>
   <si>
@@ -484,9 +470,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>27w onwards</t>
-  </si>
-  <si>
     <t>DZA</t>
   </si>
   <si>
@@ -515,10 +498,6 @@
   </si>
   <si>
     <t>Spain</t>
-  </si>
-  <si>
-    <t>27-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>EST</t>
@@ -634,9 +613,6 @@
     <t>Guatemala</t>
   </si>
   <si>
-    <t>5m onwards</t>
-  </si>
-  <si>
     <t>GUM</t>
   </si>
   <si>
@@ -727,9 +703,6 @@
     <t>Iceland</t>
   </si>
   <si>
-    <t>18w onwards</t>
-  </si>
-  <si>
     <t>ISR</t>
   </si>
   <si>
@@ -1045,10 +1018,6 @@
     <t>Netherlands (Kingdom of the)</t>
   </si>
   <si>
-    <t>22-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://rijksvaccinatieprogramma.nl/en/vaccinations/maternal-whooping-cough</t>
   </si>
   <si>
@@ -1056,10 +1025,6 @@
   </si>
   <si>
     <t>Norway</t>
-  </si>
-  <si>
-    <t>24-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>NPL</t>
@@ -1241,9 +1206,6 @@
     <t>El Salvador</t>
   </si>
   <si>
-    <t>20w onwards</t>
-  </si>
-  <si>
     <t>SMR</t>
   </si>
   <si>
@@ -1296,10 +1258,6 @@
   </si>
   <si>
     <t>Sweden</t>
-  </si>
-  <si>
-    <t>16-40w</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>SWZ</t>
@@ -1520,13 +1478,33 @@
   </si>
   <si>
     <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0264410X24008120</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>28-36w</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18-36w</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>22-36w</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>24-36w</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2162,31 +2140,31 @@
     <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="43" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="42" builtinId="8"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
     <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="超链接" xfId="42" builtinId="8"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2546,19 +2524,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C54A590-6C9E-4CD6-83FD-F000EDADCBB1}">
   <dimension ref="A1:L214"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="11.625" customWidth="1"/>
-    <col min="8" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="12" width="9.625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="5" width="15.58203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.58203125" customWidth="1"/>
+    <col min="8" max="8" width="13.08203125" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.08203125" customWidth="1"/>
+    <col min="11" max="12" width="9.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2629,7 +2607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2662,7 +2640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2695,7 +2673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2728,7 +2706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2761,7 +2739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2800,7 +2778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -2833,7 +2811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2844,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2872,12 +2850,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2905,12 +2883,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2938,21 +2916,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2977,21 +2955,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -3016,12 +2994,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
         <v>44</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3049,12 +3027,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3082,21 +3060,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -3121,12 +3099,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
         <v>51</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3154,12 +3132,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
         <v>53</v>
-      </c>
-      <c r="B18" t="s">
-        <v>54</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3187,12 +3165,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3220,12 +3198,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3253,12 +3231,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3286,18 +3264,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="14.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>25</v>
@@ -3325,12 +3303,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
         <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3358,12 +3336,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3391,12 +3369,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
         <v>68</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3424,18 +3402,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="14.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>71</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>72</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>25</v>
@@ -3463,12 +3441,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
         <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3496,21 +3474,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="14.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
         <v>75</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3535,12 +3513,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
         <v>78</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3568,12 +3546,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
         <v>80</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3601,12 +3579,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
         <v>82</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3634,45 +3612,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" t="s">
         <v>84</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <f>IF(表1[[#This Row],[VaccineDose1]]=表1[[#This Row],[VaccineDose2]],表1[[#This Row],[VaccineDose1]],99)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>85</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="I32">
-        <v>2</v>
-      </c>
-      <c r="J32">
-        <v>3</v>
-      </c>
-      <c r="K32">
-        <v>3</v>
-      </c>
-      <c r="L32">
-        <f>IF(表1[[#This Row],[VaccineDose1]]=表1[[#This Row],[VaccineDose2]],表1[[#This Row],[VaccineDose1]],99)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>86</v>
-      </c>
-      <c r="B33" t="s">
-        <v>87</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3700,21 +3678,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="14.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" t="s">
         <v>88</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
         <v>89</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E34" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3739,21 +3717,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
         <v>92</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
         <v>93</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>94</v>
-      </c>
-      <c r="E35" t="s">
-        <v>95</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3778,18 +3756,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="14.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
         <v>96</v>
       </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>473</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>25</v>
@@ -3817,12 +3795,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3850,12 +3828,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3883,12 +3861,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -3916,12 +3894,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -3949,12 +3927,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3982,12 +3960,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4015,18 +3993,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="14.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
         <v>111</v>
-      </c>
-      <c r="B43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>113</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>25</v>
@@ -4054,12 +4032,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4087,12 +4065,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4120,21 +4098,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="14.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>25</v>
+        <v>158</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>472</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -4159,12 +4137,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4192,12 +4170,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4225,18 +4203,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="14.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>25</v>
@@ -4264,12 +4242,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="14.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -4303,12 +4281,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -4336,21 +4314,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>473</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4375,12 +4353,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -4408,12 +4386,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B54" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -4441,12 +4419,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -4474,18 +4452,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="14.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>25</v>
@@ -4513,12 +4491,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -4546,12 +4524,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -4579,12 +4557,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -4612,12 +4590,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -4645,21 +4623,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -4684,12 +4662,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -4717,12 +4695,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -4750,12 +4728,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -4783,12 +4761,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -4816,21 +4794,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4855,12 +4833,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -4888,12 +4866,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -4921,21 +4899,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E69" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4960,12 +4938,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B70" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -4993,12 +4971,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -5026,12 +5004,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B72" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -5059,12 +5037,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B73" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -5092,12 +5070,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -5125,12 +5103,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B75" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -5158,12 +5136,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B76" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -5191,12 +5169,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B77" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -5224,18 +5202,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="14.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B78" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>25</v>
@@ -5263,18 +5241,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="14.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>25</v>
@@ -5302,12 +5280,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -5335,18 +5313,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="14.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>25</v>
@@ -5374,18 +5352,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="14.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>25</v>
@@ -5413,12 +5391,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -5446,12 +5424,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -5479,21 +5457,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5518,12 +5496,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -5551,21 +5529,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B87" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5590,21 +5568,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5629,12 +5607,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B89" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -5662,12 +5640,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -5695,18 +5673,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="14.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>474</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>25</v>
@@ -5734,21 +5712,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5773,21 +5751,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C93">
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>473</v>
       </c>
       <c r="E93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5812,12 +5790,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -5845,12 +5823,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -5878,12 +5856,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B96" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5911,12 +5889,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B97" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -5944,12 +5922,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B98" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5977,12 +5955,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -6010,12 +5988,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B100" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -6043,12 +6021,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -6076,12 +6054,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -6109,12 +6087,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -6142,12 +6120,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -6175,12 +6153,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -6208,12 +6186,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -6241,12 +6219,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -6274,12 +6252,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -6307,12 +6285,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -6340,12 +6318,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B110" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -6373,12 +6351,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -6406,12 +6384,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="14.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B112" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -6445,21 +6423,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B113" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E113" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -6484,18 +6462,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="14.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B114" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>25</v>
@@ -6523,18 +6501,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="14.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B115" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>25</v>
@@ -6562,12 +6540,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B116" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -6595,12 +6573,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B117" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -6628,12 +6606,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B118" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -6661,12 +6639,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B119" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -6694,12 +6672,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B120" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -6727,21 +6705,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B121" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E121" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -6766,12 +6744,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B122" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -6799,12 +6777,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B123" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -6832,12 +6810,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B124" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -6865,12 +6843,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -6898,12 +6876,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -6931,12 +6909,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -6964,12 +6942,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -6997,12 +6975,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -7030,12 +7008,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -7063,12 +7041,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -7096,12 +7074,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -7129,18 +7107,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="14.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
       <c r="D133" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>25</v>
@@ -7168,12 +7146,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -7201,12 +7179,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B135" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -7234,12 +7212,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B136" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -7267,12 +7245,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -7300,12 +7278,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B138" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -7333,12 +7311,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B139" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -7366,12 +7344,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -7399,18 +7377,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="14.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>25</v>
@@ -7438,21 +7416,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B142" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>327</v>
+        <v>475</v>
       </c>
       <c r="E142" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7477,21 +7455,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B143" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="E143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7516,12 +7494,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B144" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -7549,12 +7527,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B145" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -7582,21 +7560,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B146" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E146" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -7621,18 +7599,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="14.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B147" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>25</v>
@@ -7660,18 +7638,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="14.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B148" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>25</v>
@@ -7699,18 +7677,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="14.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B149" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>25</v>
@@ -7738,18 +7716,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="14.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B150" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>25</v>
@@ -7777,18 +7755,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="14.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B151" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>25</v>
@@ -7816,12 +7794,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B152" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -7849,12 +7827,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B153" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -7882,21 +7860,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B154" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
+        <v>41</v>
+      </c>
+      <c r="E154" t="s">
         <v>42</v>
-      </c>
-      <c r="E154" t="s">
-        <v>43</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -7921,12 +7899,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B155" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -7954,21 +7932,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B156" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -7993,18 +7971,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="14.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B157" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>25</v>
@@ -8032,12 +8010,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B158" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -8065,12 +8043,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B159" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -8098,18 +8076,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="14.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B160" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>25</v>
@@ -8137,18 +8115,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="14.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B161" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>25</v>
@@ -8176,12 +8154,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B162" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -8209,12 +8187,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B163" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -8242,18 +8220,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="14.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B164" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>25</v>
@@ -8281,12 +8259,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B165" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -8314,12 +8292,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B166" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -8347,21 +8325,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B167" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E167" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -8386,12 +8364,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B168" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -8419,12 +8397,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B169" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -8452,18 +8430,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="14.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B170" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>391</v>
+        <v>158</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>25</v>
@@ -8491,12 +8469,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B171" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -8524,12 +8502,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B172" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -8557,12 +8535,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B173" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -8590,12 +8568,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="B174" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -8623,12 +8601,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="B175" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -8656,12 +8634,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B176" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -8689,12 +8667,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="B177" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8722,21 +8700,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:12">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B178" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="E178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -8761,21 +8739,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:12">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B179" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>410</v>
+        <v>206</v>
       </c>
       <c r="E179" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8800,12 +8778,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:12">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="B180" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -8833,12 +8811,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:12">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B181" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -8866,12 +8844,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B182" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -8899,12 +8877,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B183" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -8932,12 +8910,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B184" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -8965,12 +8943,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B185" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -8998,12 +8976,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B186" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -9031,18 +9009,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="14.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B187" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>25</v>
@@ -9070,12 +9048,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B188" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -9103,12 +9081,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:12">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B189" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -9136,12 +9114,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:12">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B190" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -9169,12 +9147,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B191" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -9202,12 +9180,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B192" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -9235,12 +9213,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:12">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="B193" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -9268,12 +9246,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:12">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B194" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -9301,12 +9279,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:12">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -9334,12 +9312,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:12">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B196" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -9367,12 +9345,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:12">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B197" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -9400,12 +9378,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:12">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="B198" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -9433,12 +9411,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="B199" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -9466,18 +9444,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="14.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="B200" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>98</v>
+        <v>473</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>25</v>
@@ -9505,21 +9483,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:12">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B201" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E201" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -9544,12 +9522,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:12">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B202" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -9577,12 +9555,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:12">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B203" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -9610,12 +9588,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:12">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B204" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -9643,18 +9621,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="14.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B205" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>25</v>
@@ -9682,12 +9660,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:12">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B206" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9715,12 +9693,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:12">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B207" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9748,12 +9726,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:12">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="B208" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -9781,12 +9759,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B209" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -9814,12 +9792,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:12">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B210" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -9847,12 +9825,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:12">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B211" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -9880,21 +9858,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:12">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B212" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E212" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9919,12 +9897,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:12">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B213" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -9952,12 +9930,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:12">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B214" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -10035,5 +10013,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1389ECA-A618-4AAD-A337-BBD061424B6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1389ECA-A618-4AAD-A337-BBD061424B6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Data/VaccineSchedule.xlsx
+++ b/Data/VaccineSchedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2025/28 百日咳数据对比/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2025/28 百日咳数据对比/Project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="709" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C95ABF70-0610-4061-B0C0-FE8E490CE03B}"/>
+  <xr:revisionPtr revIDLastSave="710" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED4AAA81-4060-4DC4-A9DC-31B972608786}"/>
   <bookViews>
-    <workbookView xWindow="9280" yWindow="2090" windowWidth="28800" windowHeight="15460" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
+    <workbookView xWindow="-797" yWindow="2254" windowWidth="19423" windowHeight="12420" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
   </bookViews>
   <sheets>
     <sheet name="VaccineSchedule" sheetId="1" r:id="rId1"/>
@@ -139,9 +139,6 @@
     <t>Argentina</t>
   </si>
   <si>
-    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8876368/</t>
-  </si>
-  <si>
     <t>ARM</t>
   </si>
   <si>
@@ -1497,6 +1494,10 @@
   </si>
   <si>
     <t>24-36w</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8876368/</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2822,10 +2823,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
+        <v>157</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2852,10 +2853,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2885,10 +2886,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2918,19 +2919,19 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2957,19 +2958,19 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>40</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2996,10 +2997,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
         <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3029,10 +3030,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3062,19 +3063,19 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -3101,10 +3102,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3134,10 +3135,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3167,10 +3168,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
         <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3200,10 +3201,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3233,10 +3234,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3266,16 +3267,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
         <v>60</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>61</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>62</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>25</v>
@@ -3305,10 +3306,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
         <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3338,10 +3339,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
         <v>65</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3371,10 +3372,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
         <v>67</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3404,16 +3405,16 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" t="s">
         <v>69</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>70</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>25</v>
@@ -3443,10 +3444,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" t="s">
         <v>72</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3476,19 +3477,19 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3515,10 +3516,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
         <v>77</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3548,10 +3549,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
         <v>79</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3581,10 +3582,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
         <v>81</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3614,10 +3615,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
         <v>83</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3647,10 +3648,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
         <v>85</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3680,19 +3681,19 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
         <v>87</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
         <v>88</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E34" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3719,19 +3720,19 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
         <v>91</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
         <v>92</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>93</v>
-      </c>
-      <c r="E35" t="s">
-        <v>94</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3758,16 +3759,16 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
         <v>95</v>
       </c>
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>25</v>
@@ -3797,10 +3798,10 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
         <v>97</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3830,10 +3831,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3863,10 +3864,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
         <v>101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -3896,10 +3897,10 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" t="s">
         <v>103</v>
-      </c>
-      <c r="B40" t="s">
-        <v>104</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -3929,10 +3930,10 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
         <v>105</v>
-      </c>
-      <c r="B41" t="s">
-        <v>106</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3962,10 +3963,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" t="s">
         <v>107</v>
-      </c>
-      <c r="B42" t="s">
-        <v>108</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -3995,16 +3996,16 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" t="s">
         <v>109</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
         <v>110</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>25</v>
@@ -4034,10 +4035,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
         <v>112</v>
-      </c>
-      <c r="B44" t="s">
-        <v>113</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4067,10 +4068,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s">
         <v>114</v>
-      </c>
-      <c r="B45" t="s">
-        <v>115</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4100,19 +4101,19 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
         <v>116</v>
       </c>
-      <c r="B46" t="s">
-        <v>117</v>
-      </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -4139,10 +4140,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s">
         <v>118</v>
-      </c>
-      <c r="B47" t="s">
-        <v>119</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4172,10 +4173,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
         <v>120</v>
-      </c>
-      <c r="B48" t="s">
-        <v>121</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4205,16 +4206,16 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s">
         <v>122</v>
       </c>
-      <c r="B49" t="s">
-        <v>123</v>
-      </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>25</v>
@@ -4244,10 +4245,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s">
         <v>124</v>
-      </c>
-      <c r="B50" t="s">
-        <v>125</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -4283,10 +4284,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s">
         <v>126</v>
-      </c>
-      <c r="B51" t="s">
-        <v>127</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -4316,19 +4317,19 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4355,10 +4356,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s">
         <v>130</v>
-      </c>
-      <c r="B53" t="s">
-        <v>131</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -4388,10 +4389,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
         <v>132</v>
-      </c>
-      <c r="B54" t="s">
-        <v>133</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -4421,10 +4422,10 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s">
         <v>134</v>
-      </c>
-      <c r="B55" t="s">
-        <v>135</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -4454,16 +4455,16 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s">
         <v>136</v>
       </c>
-      <c r="B56" t="s">
-        <v>137</v>
-      </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>25</v>
@@ -4493,10 +4494,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s">
         <v>138</v>
-      </c>
-      <c r="B57" t="s">
-        <v>139</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -4526,10 +4527,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
         <v>140</v>
-      </c>
-      <c r="B58" t="s">
-        <v>141</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -4559,10 +4560,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s">
         <v>142</v>
-      </c>
-      <c r="B59" t="s">
-        <v>143</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -4592,10 +4593,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s">
         <v>144</v>
-      </c>
-      <c r="B60" t="s">
-        <v>145</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -4625,19 +4626,19 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s">
         <v>146</v>
       </c>
-      <c r="B61" t="s">
-        <v>147</v>
-      </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" t="s">
         <v>41</v>
-      </c>
-      <c r="E61" t="s">
-        <v>42</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -4664,10 +4665,10 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s">
         <v>148</v>
-      </c>
-      <c r="B62" t="s">
-        <v>149</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -4697,10 +4698,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s">
         <v>150</v>
-      </c>
-      <c r="B63" t="s">
-        <v>151</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -4730,10 +4731,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s">
         <v>152</v>
-      </c>
-      <c r="B64" t="s">
-        <v>153</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -4763,10 +4764,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s">
         <v>154</v>
-      </c>
-      <c r="B65" t="s">
-        <v>155</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -4796,19 +4797,19 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s">
         <v>156</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
         <v>157</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
-        <v>158</v>
-      </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4835,10 +4836,10 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
         <v>159</v>
-      </c>
-      <c r="B67" t="s">
-        <v>160</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -4868,10 +4869,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s">
         <v>161</v>
-      </c>
-      <c r="B68" t="s">
-        <v>162</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -4901,19 +4902,19 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s">
         <v>163</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
         <v>164</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>165</v>
-      </c>
-      <c r="E69" t="s">
-        <v>166</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4940,10 +4941,10 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>166</v>
+      </c>
+      <c r="B70" t="s">
         <v>167</v>
-      </c>
-      <c r="B70" t="s">
-        <v>168</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -4973,10 +4974,10 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s">
         <v>169</v>
-      </c>
-      <c r="B71" t="s">
-        <v>170</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -5006,10 +5007,10 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" t="s">
         <v>171</v>
-      </c>
-      <c r="B72" t="s">
-        <v>172</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -5039,10 +5040,10 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" t="s">
         <v>173</v>
-      </c>
-      <c r="B73" t="s">
-        <v>174</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -5072,10 +5073,10 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" t="s">
         <v>175</v>
-      </c>
-      <c r="B74" t="s">
-        <v>176</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -5105,10 +5106,10 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" t="s">
         <v>177</v>
-      </c>
-      <c r="B75" t="s">
-        <v>178</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -5138,10 +5139,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" t="s">
         <v>179</v>
-      </c>
-      <c r="B76" t="s">
-        <v>180</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -5171,10 +5172,10 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>180</v>
+      </c>
+      <c r="B77" t="s">
         <v>181</v>
-      </c>
-      <c r="B77" t="s">
-        <v>182</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -5204,16 +5205,16 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
         <v>183</v>
       </c>
-      <c r="B78" t="s">
-        <v>184</v>
-      </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>25</v>
@@ -5243,16 +5244,16 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" t="s">
         <v>185</v>
       </c>
-      <c r="B79" t="s">
-        <v>186</v>
-      </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>25</v>
@@ -5282,10 +5283,10 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>186</v>
+      </c>
+      <c r="B80" t="s">
         <v>187</v>
-      </c>
-      <c r="B80" t="s">
-        <v>188</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -5315,16 +5316,16 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>188</v>
+      </c>
+      <c r="B81" t="s">
         <v>189</v>
       </c>
-      <c r="B81" t="s">
-        <v>190</v>
-      </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>25</v>
@@ -5354,16 +5355,16 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>190</v>
+      </c>
+      <c r="B82" t="s">
         <v>191</v>
       </c>
-      <c r="B82" t="s">
-        <v>192</v>
-      </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>25</v>
@@ -5393,10 +5394,10 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>192</v>
+      </c>
+      <c r="B83" t="s">
         <v>193</v>
-      </c>
-      <c r="B83" t="s">
-        <v>194</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -5426,10 +5427,10 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>194</v>
+      </c>
+      <c r="B84" t="s">
         <v>195</v>
-      </c>
-      <c r="B84" t="s">
-        <v>196</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -5459,19 +5460,19 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>196</v>
+      </c>
+      <c r="B85" t="s">
         <v>197</v>
       </c>
-      <c r="B85" t="s">
-        <v>198</v>
-      </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5498,10 +5499,10 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" t="s">
         <v>199</v>
-      </c>
-      <c r="B86" t="s">
-        <v>200</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -5531,19 +5532,19 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" t="s">
         <v>201</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" t="s">
         <v>202</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E87" t="s">
-        <v>203</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5570,19 +5571,19 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>203</v>
+      </c>
+      <c r="B88" t="s">
         <v>204</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
         <v>205</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="E88" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5609,10 +5610,10 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>207</v>
+      </c>
+      <c r="B89" t="s">
         <v>208</v>
-      </c>
-      <c r="B89" t="s">
-        <v>209</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -5642,10 +5643,10 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>209</v>
+      </c>
+      <c r="B90" t="s">
         <v>210</v>
-      </c>
-      <c r="B90" t="s">
-        <v>211</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -5675,16 +5676,16 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" t="s">
         <v>212</v>
       </c>
-      <c r="B91" t="s">
-        <v>213</v>
-      </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>25</v>
@@ -5714,19 +5715,19 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>213</v>
+      </c>
+      <c r="B92" t="s">
         <v>214</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>40</v>
+      </c>
+      <c r="E92" t="s">
         <v>215</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>41</v>
-      </c>
-      <c r="E92" t="s">
-        <v>216</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5753,19 +5754,19 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
         <v>217</v>
       </c>
-      <c r="B93" t="s">
-        <v>218</v>
-      </c>
       <c r="C93">
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5792,10 +5793,10 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" t="s">
         <v>219</v>
-      </c>
-      <c r="B94" t="s">
-        <v>220</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -5825,10 +5826,10 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>220</v>
+      </c>
+      <c r="B95" t="s">
         <v>221</v>
-      </c>
-      <c r="B95" t="s">
-        <v>222</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -5858,10 +5859,10 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" t="s">
         <v>223</v>
-      </c>
-      <c r="B96" t="s">
-        <v>224</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5891,10 +5892,10 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" t="s">
         <v>225</v>
-      </c>
-      <c r="B97" t="s">
-        <v>226</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -5924,10 +5925,10 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" t="s">
         <v>227</v>
-      </c>
-      <c r="B98" t="s">
-        <v>228</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5957,10 +5958,10 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>228</v>
+      </c>
+      <c r="B99" t="s">
         <v>229</v>
-      </c>
-      <c r="B99" t="s">
-        <v>230</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -5990,10 +5991,10 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>230</v>
+      </c>
+      <c r="B100" t="s">
         <v>231</v>
-      </c>
-      <c r="B100" t="s">
-        <v>232</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -6023,10 +6024,10 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B101" t="s">
         <v>233</v>
-      </c>
-      <c r="B101" t="s">
-        <v>234</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -6056,10 +6057,10 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>234</v>
+      </c>
+      <c r="B102" t="s">
         <v>235</v>
-      </c>
-      <c r="B102" t="s">
-        <v>236</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -6089,10 +6090,10 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" t="s">
         <v>237</v>
-      </c>
-      <c r="B103" t="s">
-        <v>238</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -6122,10 +6123,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104" t="s">
         <v>239</v>
-      </c>
-      <c r="B104" t="s">
-        <v>240</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -6155,10 +6156,10 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
         <v>241</v>
-      </c>
-      <c r="B105" t="s">
-        <v>242</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -6188,10 +6189,10 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
         <v>243</v>
-      </c>
-      <c r="B106" t="s">
-        <v>244</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -6221,10 +6222,10 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
         <v>245</v>
-      </c>
-      <c r="B107" t="s">
-        <v>246</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -6254,10 +6255,10 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" t="s">
         <v>247</v>
-      </c>
-      <c r="B108" t="s">
-        <v>248</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -6287,10 +6288,10 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>248</v>
+      </c>
+      <c r="B109" t="s">
         <v>249</v>
-      </c>
-      <c r="B109" t="s">
-        <v>250</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -6320,10 +6321,10 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" t="s">
         <v>251</v>
-      </c>
-      <c r="B110" t="s">
-        <v>252</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -6353,10 +6354,10 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" t="s">
         <v>253</v>
-      </c>
-      <c r="B111" t="s">
-        <v>254</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -6386,10 +6387,10 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>254</v>
+      </c>
+      <c r="B112" t="s">
         <v>255</v>
-      </c>
-      <c r="B112" t="s">
-        <v>256</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -6425,19 +6426,19 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
         <v>257</v>
       </c>
-      <c r="B113" t="s">
-        <v>258</v>
-      </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -6464,16 +6465,16 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" t="s">
         <v>259</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="s">
         <v>260</v>
-      </c>
-      <c r="C114">
-        <v>1</v>
-      </c>
-      <c r="D114" t="s">
-        <v>261</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>25</v>
@@ -6503,16 +6504,16 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>261</v>
+      </c>
+      <c r="B115" t="s">
         <v>262</v>
       </c>
-      <c r="B115" t="s">
-        <v>263</v>
-      </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>25</v>
@@ -6542,10 +6543,10 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>263</v>
+      </c>
+      <c r="B116" t="s">
         <v>264</v>
-      </c>
-      <c r="B116" t="s">
-        <v>265</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -6575,10 +6576,10 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>265</v>
+      </c>
+      <c r="B117" t="s">
         <v>266</v>
-      </c>
-      <c r="B117" t="s">
-        <v>267</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -6608,10 +6609,10 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>267</v>
+      </c>
+      <c r="B118" t="s">
         <v>268</v>
-      </c>
-      <c r="B118" t="s">
-        <v>269</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -6641,10 +6642,10 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>269</v>
+      </c>
+      <c r="B119" t="s">
         <v>270</v>
-      </c>
-      <c r="B119" t="s">
-        <v>271</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -6674,10 +6675,10 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>271</v>
+      </c>
+      <c r="B120" t="s">
         <v>272</v>
-      </c>
-      <c r="B120" t="s">
-        <v>273</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -6707,19 +6708,19 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>273</v>
+      </c>
+      <c r="B121" t="s">
         <v>274</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E121" t="s">
         <v>275</v>
-      </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-      <c r="D121" t="s">
-        <v>41</v>
-      </c>
-      <c r="E121" t="s">
-        <v>276</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -6746,10 +6747,10 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>276</v>
+      </c>
+      <c r="B122" t="s">
         <v>277</v>
-      </c>
-      <c r="B122" t="s">
-        <v>278</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -6779,10 +6780,10 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>278</v>
+      </c>
+      <c r="B123" t="s">
         <v>279</v>
-      </c>
-      <c r="B123" t="s">
-        <v>280</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -6812,10 +6813,10 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>280</v>
+      </c>
+      <c r="B124" t="s">
         <v>281</v>
-      </c>
-      <c r="B124" t="s">
-        <v>282</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -6845,10 +6846,10 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>282</v>
+      </c>
+      <c r="B125" t="s">
         <v>283</v>
-      </c>
-      <c r="B125" t="s">
-        <v>284</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -6878,10 +6879,10 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>284</v>
+      </c>
+      <c r="B126" t="s">
         <v>285</v>
-      </c>
-      <c r="B126" t="s">
-        <v>286</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -6911,10 +6912,10 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>286</v>
+      </c>
+      <c r="B127" t="s">
         <v>287</v>
-      </c>
-      <c r="B127" t="s">
-        <v>288</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -6944,10 +6945,10 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>288</v>
+      </c>
+      <c r="B128" t="s">
         <v>289</v>
-      </c>
-      <c r="B128" t="s">
-        <v>290</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -6977,10 +6978,10 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>290</v>
+      </c>
+      <c r="B129" t="s">
         <v>291</v>
-      </c>
-      <c r="B129" t="s">
-        <v>292</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -7010,10 +7011,10 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>292</v>
+      </c>
+      <c r="B130" t="s">
         <v>293</v>
-      </c>
-      <c r="B130" t="s">
-        <v>294</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -7043,10 +7044,10 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>294</v>
+      </c>
+      <c r="B131" t="s">
         <v>295</v>
-      </c>
-      <c r="B131" t="s">
-        <v>296</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -7076,10 +7077,10 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>296</v>
+      </c>
+      <c r="B132" t="s">
         <v>297</v>
-      </c>
-      <c r="B132" t="s">
-        <v>298</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -7109,16 +7110,16 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" t="s">
         <v>299</v>
       </c>
-      <c r="B133" t="s">
-        <v>300</v>
-      </c>
       <c r="C133">
         <v>1</v>
       </c>
       <c r="D133" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>25</v>
@@ -7148,10 +7149,10 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" t="s">
         <v>301</v>
-      </c>
-      <c r="B134" t="s">
-        <v>302</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -7181,10 +7182,10 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>302</v>
+      </c>
+      <c r="B135" t="s">
         <v>303</v>
-      </c>
-      <c r="B135" t="s">
-        <v>304</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -7214,10 +7215,10 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" t="s">
         <v>305</v>
-      </c>
-      <c r="B136" t="s">
-        <v>306</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -7247,10 +7248,10 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" t="s">
         <v>307</v>
-      </c>
-      <c r="B137" t="s">
-        <v>308</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -7280,10 +7281,10 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>308</v>
+      </c>
+      <c r="B138" t="s">
         <v>309</v>
-      </c>
-      <c r="B138" t="s">
-        <v>310</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -7313,10 +7314,10 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" t="s">
         <v>311</v>
-      </c>
-      <c r="B139" t="s">
-        <v>312</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -7346,10 +7347,10 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" t="s">
         <v>313</v>
-      </c>
-      <c r="B140" t="s">
-        <v>314</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -7379,16 +7380,16 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" t="s">
         <v>315</v>
       </c>
-      <c r="B141" t="s">
-        <v>316</v>
-      </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>25</v>
@@ -7418,19 +7419,19 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" t="s">
         <v>317</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142" t="s">
+        <v>474</v>
+      </c>
+      <c r="E142" t="s">
         <v>318</v>
-      </c>
-      <c r="C142">
-        <v>1</v>
-      </c>
-      <c r="D142" t="s">
-        <v>475</v>
-      </c>
-      <c r="E142" t="s">
-        <v>319</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7457,19 +7458,19 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" t="s">
         <v>320</v>
       </c>
-      <c r="B143" t="s">
-        <v>321</v>
-      </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7496,10 +7497,10 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" t="s">
         <v>322</v>
-      </c>
-      <c r="B144" t="s">
-        <v>323</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -7529,10 +7530,10 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" t="s">
         <v>324</v>
-      </c>
-      <c r="B145" t="s">
-        <v>325</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -7562,19 +7563,19 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" t="s">
         <v>326</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="s">
         <v>327</v>
       </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>328</v>
-      </c>
-      <c r="E146" t="s">
-        <v>329</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -7601,16 +7602,16 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>329</v>
+      </c>
+      <c r="B147" t="s">
         <v>330</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
         <v>331</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>332</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>25</v>
@@ -7640,16 +7641,16 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>332</v>
+      </c>
+      <c r="B148" t="s">
         <v>333</v>
       </c>
-      <c r="B148" t="s">
-        <v>334</v>
-      </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>25</v>
@@ -7679,16 +7680,16 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>334</v>
+      </c>
+      <c r="B149" t="s">
         <v>335</v>
       </c>
-      <c r="B149" t="s">
-        <v>336</v>
-      </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>25</v>
@@ -7718,16 +7719,16 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>336</v>
+      </c>
+      <c r="B150" t="s">
         <v>337</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150" t="s">
         <v>338</v>
-      </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-      <c r="D150" t="s">
-        <v>339</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>25</v>
@@ -7757,16 +7758,16 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>339</v>
+      </c>
+      <c r="B151" t="s">
         <v>340</v>
       </c>
-      <c r="B151" t="s">
-        <v>341</v>
-      </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>25</v>
@@ -7796,10 +7797,10 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>341</v>
+      </c>
+      <c r="B152" t="s">
         <v>342</v>
-      </c>
-      <c r="B152" t="s">
-        <v>343</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -7829,10 +7830,10 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>343</v>
+      </c>
+      <c r="B153" t="s">
         <v>344</v>
-      </c>
-      <c r="B153" t="s">
-        <v>345</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -7862,19 +7863,19 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>345</v>
+      </c>
+      <c r="B154" t="s">
         <v>346</v>
       </c>
-      <c r="B154" t="s">
-        <v>347</v>
-      </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
+        <v>40</v>
+      </c>
+      <c r="E154" t="s">
         <v>41</v>
-      </c>
-      <c r="E154" t="s">
-        <v>42</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -7901,10 +7902,10 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>347</v>
+      </c>
+      <c r="B155" t="s">
         <v>348</v>
-      </c>
-      <c r="B155" t="s">
-        <v>349</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -7934,19 +7935,19 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>349</v>
+      </c>
+      <c r="B156" t="s">
         <v>350</v>
       </c>
-      <c r="B156" t="s">
-        <v>351</v>
-      </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E156" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -7973,16 +7974,16 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>351</v>
+      </c>
+      <c r="B157" t="s">
         <v>352</v>
       </c>
-      <c r="B157" t="s">
-        <v>353</v>
-      </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>25</v>
@@ -8012,10 +8013,10 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>353</v>
+      </c>
+      <c r="B158" t="s">
         <v>354</v>
-      </c>
-      <c r="B158" t="s">
-        <v>355</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -8045,10 +8046,10 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>355</v>
+      </c>
+      <c r="B159" t="s">
         <v>356</v>
-      </c>
-      <c r="B159" t="s">
-        <v>357</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -8078,16 +8079,16 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" t="s">
         <v>358</v>
       </c>
-      <c r="B160" t="s">
-        <v>359</v>
-      </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>25</v>
@@ -8117,16 +8118,16 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>359</v>
+      </c>
+      <c r="B161" t="s">
         <v>360</v>
       </c>
-      <c r="B161" t="s">
-        <v>361</v>
-      </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>25</v>
@@ -8156,10 +8157,10 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" t="s">
         <v>362</v>
-      </c>
-      <c r="B162" t="s">
-        <v>363</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -8189,10 +8190,10 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" t="s">
         <v>364</v>
-      </c>
-      <c r="B163" t="s">
-        <v>365</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -8222,16 +8223,16 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" t="s">
         <v>366</v>
       </c>
-      <c r="B164" t="s">
-        <v>367</v>
-      </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>25</v>
@@ -8261,10 +8262,10 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>367</v>
+      </c>
+      <c r="B165" t="s">
         <v>368</v>
-      </c>
-      <c r="B165" t="s">
-        <v>369</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -8294,10 +8295,10 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" t="s">
         <v>370</v>
-      </c>
-      <c r="B166" t="s">
-        <v>371</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -8327,19 +8328,19 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>371</v>
+      </c>
+      <c r="B167" t="s">
         <v>372</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="s">
+        <v>40</v>
+      </c>
+      <c r="E167" t="s">
         <v>373</v>
-      </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="D167" t="s">
-        <v>41</v>
-      </c>
-      <c r="E167" t="s">
-        <v>374</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -8366,10 +8367,10 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" t="s">
         <v>375</v>
-      </c>
-      <c r="B168" t="s">
-        <v>376</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -8399,10 +8400,10 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>376</v>
+      </c>
+      <c r="B169" t="s">
         <v>377</v>
-      </c>
-      <c r="B169" t="s">
-        <v>378</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -8432,16 +8433,16 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" t="s">
         <v>379</v>
       </c>
-      <c r="B170" t="s">
-        <v>380</v>
-      </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>25</v>
@@ -8471,10 +8472,10 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>380</v>
+      </c>
+      <c r="B171" t="s">
         <v>381</v>
-      </c>
-      <c r="B171" t="s">
-        <v>382</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -8504,10 +8505,10 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>382</v>
+      </c>
+      <c r="B172" t="s">
         <v>383</v>
-      </c>
-      <c r="B172" t="s">
-        <v>384</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -8537,10 +8538,10 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>384</v>
+      </c>
+      <c r="B173" t="s">
         <v>385</v>
-      </c>
-      <c r="B173" t="s">
-        <v>386</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -8570,10 +8571,10 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>386</v>
+      </c>
+      <c r="B174" t="s">
         <v>387</v>
-      </c>
-      <c r="B174" t="s">
-        <v>388</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -8603,10 +8604,10 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>388</v>
+      </c>
+      <c r="B175" t="s">
         <v>389</v>
-      </c>
-      <c r="B175" t="s">
-        <v>390</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -8636,10 +8637,10 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>390</v>
+      </c>
+      <c r="B176" t="s">
         <v>391</v>
-      </c>
-      <c r="B176" t="s">
-        <v>392</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -8669,10 +8670,10 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>392</v>
+      </c>
+      <c r="B177" t="s">
         <v>393</v>
-      </c>
-      <c r="B177" t="s">
-        <v>394</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8702,19 +8703,19 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" t="s">
         <v>395</v>
       </c>
-      <c r="B178" t="s">
-        <v>396</v>
-      </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -8741,19 +8742,19 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" t="s">
         <v>397</v>
       </c>
-      <c r="B179" t="s">
-        <v>398</v>
-      </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E179" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8780,10 +8781,10 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>398</v>
+      </c>
+      <c r="B180" t="s">
         <v>399</v>
-      </c>
-      <c r="B180" t="s">
-        <v>400</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -8813,10 +8814,10 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>400</v>
+      </c>
+      <c r="B181" t="s">
         <v>401</v>
-      </c>
-      <c r="B181" t="s">
-        <v>402</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -8846,10 +8847,10 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>402</v>
+      </c>
+      <c r="B182" t="s">
         <v>403</v>
-      </c>
-      <c r="B182" t="s">
-        <v>404</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -8879,10 +8880,10 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" t="s">
         <v>405</v>
-      </c>
-      <c r="B183" t="s">
-        <v>406</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -8912,10 +8913,10 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" t="s">
         <v>407</v>
-      </c>
-      <c r="B184" t="s">
-        <v>408</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -8945,10 +8946,10 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" t="s">
         <v>409</v>
-      </c>
-      <c r="B185" t="s">
-        <v>410</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -8978,10 +8979,10 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" t="s">
         <v>411</v>
-      </c>
-      <c r="B186" t="s">
-        <v>412</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -9011,16 +9012,16 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" t="s">
         <v>413</v>
       </c>
-      <c r="B187" t="s">
-        <v>414</v>
-      </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>25</v>
@@ -9050,10 +9051,10 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" t="s">
         <v>415</v>
-      </c>
-      <c r="B188" t="s">
-        <v>416</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -9083,10 +9084,10 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>416</v>
+      </c>
+      <c r="B189" t="s">
         <v>417</v>
-      </c>
-      <c r="B189" t="s">
-        <v>418</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -9116,10 +9117,10 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>418</v>
+      </c>
+      <c r="B190" t="s">
         <v>419</v>
-      </c>
-      <c r="B190" t="s">
-        <v>420</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -9149,10 +9150,10 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>420</v>
+      </c>
+      <c r="B191" t="s">
         <v>421</v>
-      </c>
-      <c r="B191" t="s">
-        <v>422</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -9182,10 +9183,10 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>422</v>
+      </c>
+      <c r="B192" t="s">
         <v>423</v>
-      </c>
-      <c r="B192" t="s">
-        <v>424</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -9215,10 +9216,10 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" t="s">
         <v>425</v>
-      </c>
-      <c r="B193" t="s">
-        <v>426</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -9248,10 +9249,10 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" t="s">
         <v>427</v>
-      </c>
-      <c r="B194" t="s">
-        <v>428</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -9281,10 +9282,10 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>428</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -9314,10 +9315,10 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>430</v>
+      </c>
+      <c r="B196" t="s">
         <v>431</v>
-      </c>
-      <c r="B196" t="s">
-        <v>432</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -9347,10 +9348,10 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
+        <v>432</v>
+      </c>
+      <c r="B197" t="s">
         <v>433</v>
-      </c>
-      <c r="B197" t="s">
-        <v>434</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -9380,10 +9381,10 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>434</v>
+      </c>
+      <c r="B198" t="s">
         <v>435</v>
-      </c>
-      <c r="B198" t="s">
-        <v>436</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -9413,10 +9414,10 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
+        <v>436</v>
+      </c>
+      <c r="B199" t="s">
         <v>437</v>
-      </c>
-      <c r="B199" t="s">
-        <v>438</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -9446,16 +9447,16 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>438</v>
+      </c>
+      <c r="B200" t="s">
         <v>439</v>
       </c>
-      <c r="B200" t="s">
-        <v>440</v>
-      </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>25</v>
@@ -9485,19 +9486,19 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>440</v>
+      </c>
+      <c r="B201" t="s">
         <v>441</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>40</v>
+      </c>
+      <c r="E201" t="s">
         <v>442</v>
-      </c>
-      <c r="C201">
-        <v>1</v>
-      </c>
-      <c r="D201" t="s">
-        <v>41</v>
-      </c>
-      <c r="E201" t="s">
-        <v>443</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -9524,10 +9525,10 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
+        <v>443</v>
+      </c>
+      <c r="B202" t="s">
         <v>444</v>
-      </c>
-      <c r="B202" t="s">
-        <v>445</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -9557,10 +9558,10 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>445</v>
+      </c>
+      <c r="B203" t="s">
         <v>446</v>
-      </c>
-      <c r="B203" t="s">
-        <v>447</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -9590,10 +9591,10 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>447</v>
+      </c>
+      <c r="B204" t="s">
         <v>448</v>
-      </c>
-      <c r="B204" t="s">
-        <v>449</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -9623,16 +9624,16 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>449</v>
+      </c>
+      <c r="B205" t="s">
         <v>450</v>
       </c>
-      <c r="B205" t="s">
-        <v>451</v>
-      </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>25</v>
@@ -9662,10 +9663,10 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
+        <v>451</v>
+      </c>
+      <c r="B206" t="s">
         <v>452</v>
-      </c>
-      <c r="B206" t="s">
-        <v>453</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9695,10 +9696,10 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>453</v>
+      </c>
+      <c r="B207" t="s">
         <v>454</v>
-      </c>
-      <c r="B207" t="s">
-        <v>455</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9728,10 +9729,10 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
+        <v>455</v>
+      </c>
+      <c r="B208" t="s">
         <v>456</v>
-      </c>
-      <c r="B208" t="s">
-        <v>457</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -9761,10 +9762,10 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
+        <v>457</v>
+      </c>
+      <c r="B209" t="s">
         <v>458</v>
-      </c>
-      <c r="B209" t="s">
-        <v>459</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -9794,10 +9795,10 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
+        <v>459</v>
+      </c>
+      <c r="B210" t="s">
         <v>460</v>
-      </c>
-      <c r="B210" t="s">
-        <v>461</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -9827,10 +9828,10 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
+        <v>461</v>
+      </c>
+      <c r="B211" t="s">
         <v>462</v>
-      </c>
-      <c r="B211" t="s">
-        <v>463</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -9860,19 +9861,19 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>463</v>
+      </c>
+      <c r="B212" t="s">
         <v>464</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="s">
         <v>465</v>
       </c>
-      <c r="C212">
-        <v>1</v>
-      </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>466</v>
-      </c>
-      <c r="E212" t="s">
-        <v>467</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9899,10 +9900,10 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" t="s">
         <v>468</v>
-      </c>
-      <c r="B213" t="s">
-        <v>469</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -9932,10 +9933,10 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" t="s">
         <v>470</v>
-      </c>
-      <c r="B214" t="s">
-        <v>471</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -10001,10 +10002,11 @@
     <hyperlink ref="E187" r:id="rId33" xr:uid="{9ADBE0FC-FC7D-4BE2-BE99-97885B873357}"/>
     <hyperlink ref="E200" r:id="rId34" xr:uid="{A9B267C3-A9CE-469A-845D-FB3A73708567}"/>
     <hyperlink ref="E205" r:id="rId35" xr:uid="{27174807-9DAE-4EC5-87C5-7B3A95323010}"/>
+    <hyperlink ref="E9" r:id="rId36" xr:uid="{19842B78-8F03-4932-9AFD-0E884F7C19A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId36"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Data/VaccineSchedule.xlsx
+++ b/Data/VaccineSchedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2025/28 百日咳数据对比/Project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="710" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED4AAA81-4060-4DC4-A9DC-31B972608786}"/>
+  <xr:revisionPtr revIDLastSave="711" documentId="8_{6B2C8828-AD43-45C3-B957-8962AC28D08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC357534-91CA-4978-9A49-3F288B01583F}"/>
   <bookViews>
-    <workbookView xWindow="-797" yWindow="2254" windowWidth="19423" windowHeight="12420" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15820" xr2:uid="{04EA11F9-B7BC-471A-98F9-2CFDCD6CFD79}"/>
   </bookViews>
   <sheets>
     <sheet name="VaccineSchedule" sheetId="1" r:id="rId1"/>
@@ -1505,6 +1505,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2106,7 +2109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2118,6 +2121,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2167,7 +2173,13 @@
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="176" formatCode="0.00_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="0.00_ "/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -2195,11 +2207,11 @@
     <tableColumn id="12" xr3:uid="{91A80A45-CDFC-4097-B30C-0318DEA5773D}" name="VaccinePregnantSource"/>
     <tableColumn id="4" xr3:uid="{28571980-2668-4B5D-B850-849FF73305BE}" name="VaccineAdult"/>
     <tableColumn id="5" xr3:uid="{40B31AF5-542D-4D82-B761-6464158DAF1E}" name="VaccineRisk"/>
-    <tableColumn id="6" xr3:uid="{6518DF24-B97F-4720-BA8E-2B5AC278AA41}" name="TimeLastShot"/>
-    <tableColumn id="7" xr3:uid="{0B12E78F-93A1-4BC4-8CC5-8583B74E4789}" name="TimeFirstShot"/>
+    <tableColumn id="6" xr3:uid="{6518DF24-B97F-4720-BA8E-2B5AC278AA41}" name="TimeLastShot" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{0B12E78F-93A1-4BC4-8CC5-8583B74E4789}" name="TimeFirstShot" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{024744F4-9A3D-45D3-AF1D-8742303F2F62}" name="VaccineDose1"/>
     <tableColumn id="10" xr3:uid="{4E47E6AC-697F-416A-88DC-F42D0EB077AC}" name="VaccineDose2"/>
-    <tableColumn id="11" xr3:uid="{CDC544EF-5E48-406E-875C-544F76F4E642}" name="VaccineDose" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{CDC544EF-5E48-406E-875C-544F76F4E642}" name="VaccineDose" dataDxfId="2">
       <calculatedColumnFormula>IF(表1[[#This Row],[VaccineDose1]]=表1[[#This Row],[VaccineDose2]],表1[[#This Row],[VaccineDose1]],99)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2531,8 +2543,8 @@
     <col min="3" max="5" width="15.58203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="11.58203125" customWidth="1"/>
-    <col min="8" max="8" width="13.08203125" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.08203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="5" customWidth="1"/>
     <col min="10" max="10" width="15.08203125" customWidth="1"/>
     <col min="11" max="12" width="9.58203125" customWidth="1"/>
   </cols>
@@ -2559,10 +2571,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2591,10 +2603,10 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>120</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>2</v>
       </c>
       <c r="J2">
@@ -2624,10 +2636,10 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J3">
@@ -2657,10 +2669,10 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
         <v>2</v>
       </c>
       <c r="J4">
@@ -2690,10 +2702,10 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>60</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5">
@@ -2723,10 +2735,10 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>24</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>2</v>
       </c>
       <c r="J6">
@@ -2762,10 +2774,10 @@
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>180</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>2</v>
       </c>
       <c r="J7">
@@ -2795,10 +2807,10 @@
       <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>192</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>2</v>
       </c>
       <c r="J8">
@@ -2834,10 +2846,10 @@
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>132</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>2</v>
       </c>
       <c r="J9">
@@ -2867,10 +2879,10 @@
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>192</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J10">
@@ -2900,10 +2912,10 @@
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>18</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2939,10 +2951,10 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>156</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="5">
         <v>2</v>
       </c>
       <c r="J12">
@@ -2978,10 +2990,10 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>96</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="5">
         <v>2</v>
       </c>
       <c r="J13">
@@ -3011,10 +3023,10 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>18</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="5">
         <v>2</v>
       </c>
       <c r="J14">
@@ -3044,10 +3056,10 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>18</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J15">
@@ -3083,10 +3095,10 @@
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>192</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J16">
@@ -3116,10 +3128,10 @@
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J17">
@@ -3149,10 +3161,10 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>3.6781609195402298</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J18">
@@ -3182,10 +3194,10 @@
       <c r="G19">
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J19">
@@ -3215,10 +3227,10 @@
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>144</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="5">
         <v>2</v>
       </c>
       <c r="J20">
@@ -3248,10 +3260,10 @@
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>156</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="5">
         <v>2</v>
       </c>
       <c r="J21">
@@ -3287,10 +3299,10 @@
       <c r="G22">
         <v>0</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>144</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="5">
         <v>2</v>
       </c>
       <c r="J22">
@@ -3320,10 +3332,10 @@
       <c r="G23">
         <v>0</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>84</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="5">
         <v>2</v>
       </c>
       <c r="J23">
@@ -3353,10 +3365,10 @@
       <c r="G24">
         <v>1</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>18</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="5">
         <v>2</v>
       </c>
       <c r="J24">
@@ -3386,10 +3398,10 @@
       <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>48</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="5">
         <v>2</v>
       </c>
       <c r="J25">
@@ -3425,10 +3437,10 @@
       <c r="G26">
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>216</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="5">
         <v>2</v>
       </c>
       <c r="J26">
@@ -3458,10 +3470,10 @@
       <c r="G27">
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>48</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="5">
         <v>2</v>
       </c>
       <c r="J27">
@@ -3497,10 +3509,10 @@
       <c r="G28">
         <v>1</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>48</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="5">
         <v>2</v>
       </c>
       <c r="J28">
@@ -3530,10 +3542,10 @@
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>54</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="5">
         <v>2</v>
       </c>
       <c r="J29">
@@ -3563,10 +3575,10 @@
       <c r="G30">
         <v>0</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <v>60</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="5">
         <v>2</v>
       </c>
       <c r="J30">
@@ -3596,10 +3608,10 @@
       <c r="G31">
         <v>0</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="5">
         <v>24</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J31">
@@ -3629,10 +3641,10 @@
       <c r="G32">
         <v>0</v>
       </c>
-      <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="I32">
+      <c r="H32" s="5">
+        <v>4</v>
+      </c>
+      <c r="I32" s="5">
         <v>2</v>
       </c>
       <c r="J32">
@@ -3662,10 +3674,10 @@
       <c r="G33">
         <v>0</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J33">
@@ -3701,10 +3713,10 @@
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="5">
         <v>192</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="5">
         <v>2</v>
       </c>
       <c r="J34">
@@ -3740,10 +3752,10 @@
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="5">
         <v>180</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="5">
         <v>2</v>
       </c>
       <c r="J35">
@@ -3779,10 +3791,10 @@
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="5">
         <v>156</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="5">
         <v>2</v>
       </c>
       <c r="J36">
@@ -3812,10 +3824,10 @@
       <c r="G37">
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="5">
         <v>18</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="5">
         <v>3</v>
       </c>
       <c r="J37">
@@ -3845,10 +3857,10 @@
       <c r="G38">
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J38">
@@ -3878,10 +3890,10 @@
       <c r="G39">
         <v>0</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J39">
@@ -3911,10 +3923,10 @@
       <c r="G40">
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J40">
@@ -3944,10 +3956,10 @@
       <c r="G41">
         <v>0</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="5">
         <v>3.6781609195402298</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J41">
@@ -3977,10 +3989,10 @@
       <c r="G42">
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="5">
         <v>48</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J42">
@@ -4016,10 +4028,10 @@
       <c r="G43">
         <v>1</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="5">
         <v>18</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="5">
         <v>2</v>
       </c>
       <c r="J43">
@@ -4049,10 +4061,10 @@
       <c r="G44">
         <v>0</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J44">
@@ -4082,10 +4094,10 @@
       <c r="G45">
         <v>0</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="5">
         <v>18</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="5">
         <v>2</v>
       </c>
       <c r="J45">
@@ -4121,10 +4133,10 @@
       <c r="G46">
         <v>1</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="5">
         <v>48</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="5">
         <v>2</v>
       </c>
       <c r="J46">
@@ -4154,10 +4166,10 @@
       <c r="G47">
         <v>1</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="5">
         <v>18</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="5">
         <v>2</v>
       </c>
       <c r="J47">
@@ -4187,10 +4199,10 @@
       <c r="G48">
         <v>0</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="5">
         <v>15</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="5">
         <v>2</v>
       </c>
       <c r="J48">
@@ -4226,10 +4238,10 @@
       <c r="G49">
         <v>0</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="5">
         <v>192</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="5">
         <v>2</v>
       </c>
       <c r="J49">
@@ -4265,10 +4277,10 @@
       <c r="G50">
         <v>0</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="5">
         <v>144</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="5">
         <v>2</v>
       </c>
       <c r="J50">
@@ -4298,10 +4310,10 @@
       <c r="G51">
         <v>0</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="5">
         <v>120</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="5">
         <v>3</v>
       </c>
       <c r="J51">
@@ -4337,10 +4349,10 @@
       <c r="G52">
         <v>1</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="5">
         <v>192</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="5">
         <v>2</v>
       </c>
       <c r="J52">
@@ -4370,10 +4382,10 @@
       <c r="G53">
         <v>0</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="5">
         <v>15</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J53">
@@ -4403,10 +4415,10 @@
       <c r="G54">
         <v>0</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="5">
         <v>36</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="5">
         <v>2</v>
       </c>
       <c r="J54">
@@ -4436,10 +4448,10 @@
       <c r="G55">
         <v>0</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="5">
         <v>60</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="5">
         <v>3</v>
       </c>
       <c r="J55">
@@ -4475,10 +4487,10 @@
       <c r="G56">
         <v>1</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="5">
         <v>48</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="5">
         <v>2</v>
       </c>
       <c r="J56">
@@ -4508,10 +4520,10 @@
       <c r="G57">
         <v>0</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="5">
         <v>72</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="5">
         <v>2</v>
       </c>
       <c r="J57">
@@ -4541,10 +4553,10 @@
       <c r="G58">
         <v>0</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="5">
         <v>60</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="5">
         <v>2</v>
       </c>
       <c r="J58">
@@ -4574,10 +4586,10 @@
       <c r="G59">
         <v>0</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="5">
         <v>18</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="5">
         <v>2</v>
       </c>
       <c r="J59">
@@ -4607,10 +4619,10 @@
       <c r="G60">
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J60">
@@ -4646,10 +4658,10 @@
       <c r="G61">
         <v>1</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="5">
         <v>72</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="5">
         <v>2</v>
       </c>
       <c r="J61">
@@ -4679,10 +4691,10 @@
       <c r="G62">
         <v>0</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="5">
         <v>192</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="5">
         <v>3</v>
       </c>
       <c r="J62">
@@ -4712,10 +4724,10 @@
       <c r="G63">
         <v>0</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J63">
@@ -4745,10 +4757,10 @@
       <c r="G64">
         <v>0</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="5">
         <v>180</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="5">
         <v>3</v>
       </c>
       <c r="J64">
@@ -4778,10 +4790,10 @@
       <c r="G65">
         <v>0</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J65">
@@ -4817,10 +4829,10 @@
       <c r="G66">
         <v>0</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="5">
         <v>156</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="5">
         <v>2</v>
       </c>
       <c r="J66">
@@ -4850,10 +4862,10 @@
       <c r="G67">
         <v>0</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="5">
         <v>144</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="5">
         <v>2</v>
       </c>
       <c r="J67">
@@ -4883,10 +4895,10 @@
       <c r="G68">
         <v>0</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J68">
@@ -4922,10 +4934,10 @@
       <c r="G69">
         <v>0</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="5">
         <v>40</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J69">
@@ -4955,10 +4967,10 @@
       <c r="G70">
         <v>0</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="5">
         <v>60</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="5">
         <v>2</v>
       </c>
       <c r="J70">
@@ -4988,10 +5000,10 @@
       <c r="G71">
         <v>0</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J71">
@@ -5021,10 +5033,10 @@
       <c r="G72">
         <v>0</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J72">
@@ -5054,10 +5066,10 @@
       <c r="G73">
         <v>0</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="5">
         <v>18</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="5">
         <v>2</v>
       </c>
       <c r="J73">
@@ -5087,10 +5099,10 @@
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J74">
@@ -5120,10 +5132,10 @@
       <c r="G75">
         <v>0</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="5">
         <v>18</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J75">
@@ -5153,10 +5165,10 @@
       <c r="G76">
         <v>0</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="5">
         <v>144</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="5">
         <v>2</v>
       </c>
       <c r="J76">
@@ -5186,10 +5198,10 @@
       <c r="G77">
         <v>0</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="5">
         <v>18</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J77">
@@ -5225,10 +5237,10 @@
       <c r="G78">
         <v>1</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="5">
         <v>48</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="5">
         <v>2</v>
       </c>
       <c r="J78">
@@ -5264,10 +5276,10 @@
       <c r="G79">
         <v>0</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="5">
         <v>132</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="5">
         <v>2</v>
       </c>
       <c r="J79">
@@ -5297,10 +5309,10 @@
       <c r="G80">
         <v>0</v>
       </c>
-      <c r="H80">
-        <v>6</v>
-      </c>
-      <c r="I80">
+      <c r="H80" s="5">
+        <v>6</v>
+      </c>
+      <c r="I80" s="5">
         <v>2</v>
       </c>
       <c r="J80">
@@ -5336,10 +5348,10 @@
       <c r="G81">
         <v>0</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="5">
         <v>132</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="5">
         <v>2</v>
       </c>
       <c r="J81">
@@ -5375,10 +5387,10 @@
       <c r="G82">
         <v>1</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="5">
         <v>48</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="5">
         <v>2</v>
       </c>
       <c r="J82">
@@ -5408,10 +5420,10 @@
       <c r="G83">
         <v>0</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="5">
         <v>72</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="5">
         <v>2</v>
       </c>
       <c r="J83">
@@ -5441,10 +5453,10 @@
       <c r="G84">
         <v>0</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="5">
         <v>15</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J84">
@@ -5480,10 +5492,10 @@
       <c r="G85">
         <v>0</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="5">
         <v>132</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="5">
         <v>2</v>
       </c>
       <c r="J85">
@@ -5513,10 +5525,10 @@
       <c r="G86">
         <v>0</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="5">
         <v>18</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="5">
         <v>2</v>
       </c>
       <c r="J86">
@@ -5552,10 +5564,10 @@
       <c r="G87">
         <v>0</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="5">
         <v>72</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J87">
@@ -5591,10 +5603,10 @@
       <c r="G88">
         <v>1</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="5">
         <v>156</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="5">
         <v>2</v>
       </c>
       <c r="J88">
@@ -5624,10 +5636,10 @@
       <c r="G89">
         <v>0</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="5">
         <v>72</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="5">
         <v>2</v>
       </c>
       <c r="J89">
@@ -5657,10 +5669,10 @@
       <c r="G90">
         <v>0</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="5">
         <v>72</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="5">
         <v>2</v>
       </c>
       <c r="J90">
@@ -5696,10 +5708,10 @@
       <c r="G91">
         <v>0</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="5">
         <v>168</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="5">
         <v>3</v>
       </c>
       <c r="J91">
@@ -5735,10 +5747,10 @@
       <c r="G92">
         <v>1</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="5">
         <v>156</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="5">
         <v>2</v>
       </c>
       <c r="J92">
@@ -5774,10 +5786,10 @@
       <c r="G93">
         <v>0</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="5">
         <v>216</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="5">
         <v>3</v>
       </c>
       <c r="J93">
@@ -5807,10 +5819,10 @@
       <c r="G94">
         <v>0</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="5">
         <v>72</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J94">
@@ -5840,10 +5852,10 @@
       <c r="G95">
         <v>0</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="5">
         <v>18</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="5">
         <v>3</v>
       </c>
       <c r="J95">
@@ -5873,10 +5885,10 @@
       <c r="G96">
         <v>0</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="5">
         <v>18</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="5">
         <v>3</v>
       </c>
       <c r="J96">
@@ -5906,10 +5918,10 @@
       <c r="G97">
         <v>0</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="5">
         <v>72</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="5">
         <v>2</v>
       </c>
       <c r="J97">
@@ -5939,10 +5951,10 @@
       <c r="G98">
         <v>0</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J98">
@@ -5972,10 +5984,10 @@
       <c r="G99">
         <v>0</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="5">
         <v>24</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="5">
         <v>2</v>
       </c>
       <c r="J99">
@@ -6005,10 +6017,10 @@
       <c r="G100">
         <v>0</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J100">
@@ -6038,10 +6050,10 @@
       <c r="G101">
         <v>0</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="5">
         <v>72</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J101">
@@ -6071,10 +6083,10 @@
       <c r="G102">
         <v>0</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="5">
         <v>60</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="5">
         <v>2</v>
       </c>
       <c r="J102">
@@ -6104,10 +6116,10 @@
       <c r="G103">
         <v>0</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="5">
         <v>144</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="5">
         <v>2</v>
       </c>
       <c r="J103">
@@ -6137,10 +6149,10 @@
       <c r="G104">
         <v>0</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="5">
         <v>43.2</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="5">
         <v>2</v>
       </c>
       <c r="J104">
@@ -6170,10 +6182,10 @@
       <c r="G105">
         <v>0</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J105">
@@ -6203,10 +6215,10 @@
       <c r="G106">
         <v>0</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="5">
         <v>60</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="5">
         <v>2</v>
       </c>
       <c r="J106">
@@ -6236,10 +6248,10 @@
       <c r="G107">
         <v>0</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J107">
@@ -6269,10 +6281,10 @@
       <c r="G108">
         <v>0</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="5">
         <v>180</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="5">
         <v>2</v>
       </c>
       <c r="J108">
@@ -6302,10 +6314,10 @@
       <c r="G109">
         <v>0</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="5">
         <v>60</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="5">
         <v>2</v>
       </c>
       <c r="J109">
@@ -6335,10 +6347,10 @@
       <c r="G110">
         <v>0</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="5">
         <v>18</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="5">
         <v>2</v>
       </c>
       <c r="J110">
@@ -6368,10 +6380,10 @@
       <c r="G111">
         <v>0</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J111">
@@ -6407,10 +6419,10 @@
       <c r="G112">
         <v>0</v>
       </c>
-      <c r="H112">
+      <c r="H112" s="5">
         <v>192</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="5">
         <v>2</v>
       </c>
       <c r="J112">
@@ -6446,10 +6458,10 @@
       <c r="G113">
         <v>0</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="5">
         <v>192</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="5">
         <v>2</v>
       </c>
       <c r="J113">
@@ -6485,10 +6497,10 @@
       <c r="G114">
         <v>1</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="5">
         <v>168</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="5">
         <v>2</v>
       </c>
       <c r="J114">
@@ -6524,10 +6536,10 @@
       <c r="G115">
         <v>1</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="5">
         <v>144</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="5">
         <v>2</v>
       </c>
       <c r="J115">
@@ -6557,10 +6569,10 @@
       <c r="G116">
         <v>0</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="5">
         <v>60</v>
       </c>
-      <c r="I116">
+      <c r="I116" s="5">
         <v>2</v>
       </c>
       <c r="J116">
@@ -6590,10 +6602,10 @@
       <c r="G117">
         <v>0</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="5">
         <v>156</v>
       </c>
-      <c r="I117">
+      <c r="I117" s="5">
         <v>2</v>
       </c>
       <c r="J117">
@@ -6623,10 +6635,10 @@
       <c r="G118">
         <v>0</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="5">
         <v>24</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="5">
         <v>2</v>
       </c>
       <c r="J118">
@@ -6656,10 +6668,10 @@
       <c r="G119">
         <v>0</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J119">
@@ -6689,10 +6701,10 @@
       <c r="G120">
         <v>0</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="5">
         <v>48</v>
       </c>
-      <c r="I120">
+      <c r="I120" s="5">
         <v>2</v>
       </c>
       <c r="J120">
@@ -6728,10 +6740,10 @@
       <c r="G121">
         <v>0</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="5">
         <v>48</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="5">
         <v>2</v>
       </c>
       <c r="J121">
@@ -6761,10 +6773,10 @@
       <c r="G122">
         <v>0</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="5">
         <v>144</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="5">
         <v>2</v>
       </c>
       <c r="J122">
@@ -6794,10 +6806,10 @@
       <c r="G123">
         <v>0</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="5">
         <v>84</v>
       </c>
-      <c r="I123">
+      <c r="I123" s="5">
         <v>2</v>
       </c>
       <c r="J123">
@@ -6827,10 +6839,10 @@
       <c r="G124">
         <v>0</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I124">
+      <c r="I124" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J124">
@@ -6860,10 +6872,10 @@
       <c r="G125">
         <v>0</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="5">
         <v>18</v>
       </c>
-      <c r="I125">
+      <c r="I125" s="5">
         <v>2</v>
       </c>
       <c r="J125">
@@ -6893,10 +6905,10 @@
       <c r="G126">
         <v>0</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="5">
         <v>18</v>
       </c>
-      <c r="I126">
+      <c r="I126" s="5">
         <v>2</v>
       </c>
       <c r="J126">
@@ -6926,10 +6938,10 @@
       <c r="G127">
         <v>0</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="5">
         <v>72</v>
       </c>
-      <c r="I127">
+      <c r="I127" s="5">
         <v>2.0689655172413799</v>
       </c>
       <c r="J127">
@@ -6959,10 +6971,10 @@
       <c r="G128">
         <v>0</v>
       </c>
-      <c r="H128">
-        <v>4</v>
-      </c>
-      <c r="I128">
+      <c r="H128" s="5">
+        <v>4</v>
+      </c>
+      <c r="I128" s="5">
         <v>2</v>
       </c>
       <c r="J128">
@@ -6992,10 +7004,10 @@
       <c r="G129">
         <v>0</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="5">
         <v>216</v>
       </c>
-      <c r="I129">
+      <c r="I129" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J129">
@@ -7025,10 +7037,10 @@
       <c r="G130">
         <v>0</v>
       </c>
-      <c r="H130">
-        <v>4</v>
-      </c>
-      <c r="I130">
+      <c r="H130" s="5">
+        <v>4</v>
+      </c>
+      <c r="I130" s="5">
         <v>2</v>
       </c>
       <c r="J130">
@@ -7058,10 +7070,10 @@
       <c r="G131">
         <v>0</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I131">
+      <c r="I131" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J131">
@@ -7091,10 +7103,10 @@
       <c r="G132">
         <v>0</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="5">
         <v>18</v>
       </c>
-      <c r="I132">
+      <c r="I132" s="5">
         <v>2</v>
       </c>
       <c r="J132">
@@ -7130,10 +7142,10 @@
       <c r="G133">
         <v>0</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="5">
         <v>132</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J133">
@@ -7163,10 +7175,10 @@
       <c r="G134">
         <v>0</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I134">
+      <c r="I134" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J134">
@@ -7196,10 +7208,10 @@
       <c r="G135">
         <v>0</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="5">
         <v>18</v>
       </c>
-      <c r="I135">
+      <c r="I135" s="5">
         <v>2</v>
       </c>
       <c r="J135">
@@ -7229,10 +7241,10 @@
       <c r="G136">
         <v>0</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I136">
+      <c r="I136" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J136">
@@ -7262,10 +7274,10 @@
       <c r="G137">
         <v>0</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="5">
         <v>132</v>
       </c>
-      <c r="I137">
+      <c r="I137" s="5">
         <v>2</v>
       </c>
       <c r="J137">
@@ -7295,10 +7307,10 @@
       <c r="G138">
         <v>0</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I138">
+      <c r="I138" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J138">
@@ -7328,10 +7340,10 @@
       <c r="G139">
         <v>0</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I139">
+      <c r="I139" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J139">
@@ -7361,10 +7373,10 @@
       <c r="G140">
         <v>0</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="5">
         <v>72</v>
       </c>
-      <c r="I140">
+      <c r="I140" s="5">
         <v>2</v>
       </c>
       <c r="J140">
@@ -7400,10 +7412,10 @@
       <c r="G141">
         <v>0</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="5">
         <v>132</v>
       </c>
-      <c r="I141">
+      <c r="I141" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J141">
@@ -7439,10 +7451,10 @@
       <c r="G142">
         <v>1</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="5">
         <v>48</v>
       </c>
-      <c r="I142">
+      <c r="I142" s="5">
         <v>3</v>
       </c>
       <c r="J142">
@@ -7478,10 +7490,10 @@
       <c r="G143">
         <v>1</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="5">
         <v>180</v>
       </c>
-      <c r="I143">
+      <c r="I143" s="5">
         <v>3</v>
       </c>
       <c r="J143">
@@ -7511,10 +7523,10 @@
       <c r="G144">
         <v>0</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I144">
+      <c r="I144" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J144">
@@ -7544,10 +7556,10 @@
       <c r="G145">
         <v>0</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="5">
         <v>48</v>
       </c>
-      <c r="I145">
+      <c r="I145" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J145">
@@ -7583,10 +7595,10 @@
       <c r="G146">
         <v>1</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="5">
         <v>156</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J146">
@@ -7622,10 +7634,10 @@
       <c r="G147">
         <v>1</v>
       </c>
-      <c r="H147">
+      <c r="H147" s="5">
         <v>18</v>
       </c>
-      <c r="I147">
+      <c r="I147" s="5">
         <v>2</v>
       </c>
       <c r="J147">
@@ -7661,10 +7673,10 @@
       <c r="G148">
         <v>0</v>
       </c>
-      <c r="H148">
+      <c r="H148" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I148">
+      <c r="I148" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J148">
@@ -7700,10 +7712,10 @@
       <c r="G149">
         <v>1</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="5">
         <v>120</v>
       </c>
-      <c r="I149">
+      <c r="I149" s="5">
         <v>2</v>
       </c>
       <c r="J149">
@@ -7739,10 +7751,10 @@
       <c r="G150">
         <v>0</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="5">
         <v>48</v>
       </c>
-      <c r="I150">
+      <c r="I150" s="5">
         <v>2</v>
       </c>
       <c r="J150">
@@ -7778,10 +7790,10 @@
       <c r="G151">
         <v>0</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I151">
+      <c r="I151" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J151">
@@ -7811,10 +7823,10 @@
       <c r="G152">
         <v>0</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="5">
         <v>120</v>
       </c>
-      <c r="I152">
+      <c r="I152" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J152">
@@ -7844,10 +7856,10 @@
       <c r="G153">
         <v>0</v>
       </c>
-      <c r="H153">
-        <v>3</v>
-      </c>
-      <c r="I153">
+      <c r="H153" s="5">
+        <v>3</v>
+      </c>
+      <c r="I153" s="5">
         <v>1</v>
       </c>
       <c r="J153">
@@ -7883,10 +7895,10 @@
       <c r="G154">
         <v>1</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="5">
         <v>168</v>
       </c>
-      <c r="I154">
+      <c r="I154" s="5">
         <v>1.6091954022988499</v>
       </c>
       <c r="J154">
@@ -7916,10 +7928,10 @@
       <c r="G155">
         <v>0</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I155">
+      <c r="I155" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J155">
@@ -7955,10 +7967,10 @@
       <c r="G156">
         <v>0</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="5">
         <v>60</v>
       </c>
-      <c r="I156">
+      <c r="I156" s="5">
         <v>2</v>
       </c>
       <c r="J156">
@@ -7994,10 +8006,10 @@
       <c r="G157">
         <v>1</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="5">
         <v>120</v>
       </c>
-      <c r="I157">
+      <c r="I157" s="5">
         <v>2</v>
       </c>
       <c r="J157">
@@ -8027,10 +8039,10 @@
       <c r="G158">
         <v>0</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="5">
         <v>18</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="5">
         <v>2</v>
       </c>
       <c r="J158">
@@ -8060,10 +8072,10 @@
       <c r="G159">
         <v>0</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="5">
         <v>132</v>
       </c>
-      <c r="I159">
+      <c r="I159" s="5">
         <v>2</v>
       </c>
       <c r="J159">
@@ -8099,10 +8111,10 @@
       <c r="G160">
         <v>0</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="5">
         <v>216</v>
       </c>
-      <c r="I160">
+      <c r="I160" s="5">
         <v>2</v>
       </c>
       <c r="J160">
@@ -8138,10 +8150,10 @@
       <c r="G161">
         <v>0</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="5">
         <v>168</v>
       </c>
-      <c r="I161">
+      <c r="I161" s="5">
         <v>2</v>
       </c>
       <c r="J161">
@@ -8171,10 +8183,10 @@
       <c r="G162">
         <v>1</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="5">
         <v>18</v>
       </c>
-      <c r="I162">
+      <c r="I162" s="5">
         <v>3</v>
       </c>
       <c r="J162">
@@ -8204,10 +8216,10 @@
       <c r="G163">
         <v>0</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I163">
+      <c r="I163" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J163">
@@ -8243,10 +8255,10 @@
       <c r="G164">
         <v>0</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="5">
         <v>72</v>
       </c>
-      <c r="I164">
+      <c r="I164" s="5">
         <v>2</v>
       </c>
       <c r="J164">
@@ -8276,10 +8288,10 @@
       <c r="G165">
         <v>0</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J165">
@@ -8309,10 +8321,10 @@
       <c r="G166">
         <v>0</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J166">
@@ -8348,10 +8360,10 @@
       <c r="G167">
         <v>0</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="5">
         <v>132</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="5">
         <v>2</v>
       </c>
       <c r="J167">
@@ -8381,10 +8393,10 @@
       <c r="G168">
         <v>0</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J168">
@@ -8414,10 +8426,10 @@
       <c r="G169">
         <v>0</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J169">
@@ -8453,10 +8465,10 @@
       <c r="G170">
         <v>1</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="5">
         <v>48</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="5">
         <v>2</v>
       </c>
       <c r="J170">
@@ -8486,10 +8498,10 @@
       <c r="G171">
         <v>0</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="5">
         <v>180</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="5">
         <v>3</v>
       </c>
       <c r="J171">
@@ -8519,10 +8531,10 @@
       <c r="G172">
         <v>0</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J172">
@@ -8552,10 +8564,10 @@
       <c r="G173">
         <v>0</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="5">
         <v>84</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J173">
@@ -8585,10 +8597,10 @@
       <c r="G174">
         <v>0</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J174">
@@ -8618,10 +8630,10 @@
       <c r="G175">
         <v>0</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I175">
+      <c r="I175" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J175">
@@ -8651,10 +8663,10 @@
       <c r="G176">
         <v>1</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="5">
         <v>60</v>
       </c>
-      <c r="I176">
+      <c r="I176" s="5">
         <v>2</v>
       </c>
       <c r="J176">
@@ -8684,10 +8696,10 @@
       <c r="G177">
         <v>0</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="5">
         <v>144</v>
       </c>
-      <c r="I177">
+      <c r="I177" s="5">
         <v>2</v>
       </c>
       <c r="J177">
@@ -8723,10 +8735,10 @@
       <c r="G178">
         <v>0</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="5">
         <v>96</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="5">
         <v>3</v>
       </c>
       <c r="J178">
@@ -8762,10 +8774,10 @@
       <c r="G179">
         <v>0</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="5">
         <v>192</v>
       </c>
-      <c r="I179">
+      <c r="I179" s="5">
         <v>3</v>
       </c>
       <c r="J179">
@@ -8795,10 +8807,10 @@
       <c r="G180">
         <v>0</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="5">
         <v>18</v>
       </c>
-      <c r="I180">
+      <c r="I180" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J180">
@@ -8828,10 +8840,10 @@
       <c r="G181">
         <v>0</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="5">
         <v>12</v>
       </c>
-      <c r="I181">
+      <c r="I181" s="5">
         <v>2</v>
       </c>
       <c r="J181">
@@ -8861,10 +8873,10 @@
       <c r="G182">
         <v>0</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="5">
         <v>18</v>
       </c>
-      <c r="I182">
+      <c r="I182" s="5">
         <v>3</v>
       </c>
       <c r="J182">
@@ -8894,10 +8906,10 @@
       <c r="G183">
         <v>0</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="5">
         <v>18</v>
       </c>
-      <c r="I183">
+      <c r="I183" s="5">
         <v>1.83908045977012</v>
       </c>
       <c r="J183">
@@ -8927,10 +8939,10 @@
       <c r="G184">
         <v>0</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="5">
         <v>36</v>
       </c>
-      <c r="I184">
+      <c r="I184" s="5">
         <v>2</v>
       </c>
       <c r="J184">
@@ -8960,10 +8972,10 @@
       <c r="G185">
         <v>0</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I185">
+      <c r="I185" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J185">
@@ -8993,10 +9005,10 @@
       <c r="G186">
         <v>0</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I186">
+      <c r="I186" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J186">
@@ -9032,10 +9044,10 @@
       <c r="G187">
         <v>0</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="5">
         <v>48</v>
       </c>
-      <c r="I187">
+      <c r="I187" s="5">
         <v>2</v>
       </c>
       <c r="J187">
@@ -9065,10 +9077,10 @@
       <c r="G188">
         <v>0</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="5">
         <v>23</v>
       </c>
-      <c r="I188">
+      <c r="I188" s="5">
         <v>2</v>
       </c>
       <c r="J188">
@@ -9098,10 +9110,10 @@
       <c r="G189">
         <v>0</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="5">
         <v>60</v>
       </c>
-      <c r="I189">
+      <c r="I189" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J189">
@@ -9131,10 +9143,10 @@
       <c r="G190">
         <v>0</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="5">
         <v>18</v>
       </c>
-      <c r="I190">
+      <c r="I190" s="5">
         <v>2</v>
       </c>
       <c r="J190">
@@ -9164,10 +9176,10 @@
       <c r="G191">
         <v>0</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="5">
         <v>18</v>
       </c>
-      <c r="I191">
+      <c r="I191" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J191">
@@ -9197,10 +9209,10 @@
       <c r="G192">
         <v>0</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="5">
         <v>60</v>
       </c>
-      <c r="I192">
+      <c r="I192" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J192">
@@ -9230,10 +9242,10 @@
       <c r="G193">
         <v>0</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="5">
         <v>60</v>
       </c>
-      <c r="I193">
+      <c r="I193" s="5">
         <v>2</v>
       </c>
       <c r="J193">
@@ -9263,10 +9275,10 @@
       <c r="G194">
         <v>0</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="5">
         <v>18</v>
       </c>
-      <c r="I194">
+      <c r="I194" s="5">
         <v>2</v>
       </c>
       <c r="J194">
@@ -9296,10 +9308,10 @@
       <c r="G195">
         <v>0</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="5">
         <v>48</v>
       </c>
-      <c r="I195">
+      <c r="I195" s="5">
         <v>2</v>
       </c>
       <c r="J195">
@@ -9329,10 +9341,10 @@
       <c r="G196">
         <v>0</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="5">
         <v>72</v>
       </c>
-      <c r="I196">
+      <c r="I196" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J196">
@@ -9362,10 +9374,10 @@
       <c r="G197">
         <v>0</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I197">
+      <c r="I197" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J197">
@@ -9395,10 +9407,10 @@
       <c r="G198">
         <v>0</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I198">
+      <c r="I198" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J198">
@@ -9428,10 +9440,10 @@
       <c r="G199">
         <v>0</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="5">
         <v>18</v>
       </c>
-      <c r="I199">
+      <c r="I199" s="5">
         <v>2</v>
       </c>
       <c r="J199">
@@ -9467,10 +9479,10 @@
       <c r="G200">
         <v>1</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="5">
         <v>132</v>
       </c>
-      <c r="I200">
+      <c r="I200" s="5">
         <v>2</v>
       </c>
       <c r="J200">
@@ -9506,10 +9518,10 @@
       <c r="G201">
         <v>0</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="5">
         <v>144</v>
       </c>
-      <c r="I201">
+      <c r="I201" s="5">
         <v>2</v>
       </c>
       <c r="J201">
@@ -9539,10 +9551,10 @@
       <c r="G202">
         <v>0</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="5">
         <v>16</v>
       </c>
-      <c r="I202">
+      <c r="I202" s="5">
         <v>2</v>
       </c>
       <c r="J202">
@@ -9572,10 +9584,10 @@
       <c r="G203">
         <v>0</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="5">
         <v>18</v>
       </c>
-      <c r="I203">
+      <c r="I203" s="5">
         <v>2</v>
       </c>
       <c r="J203">
@@ -9605,10 +9617,10 @@
       <c r="G204">
         <v>0</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="5">
         <v>60</v>
       </c>
-      <c r="I204">
+      <c r="I204" s="5">
         <v>2</v>
       </c>
       <c r="J204">
@@ -9644,10 +9656,10 @@
       <c r="G205">
         <v>0</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="5">
         <v>48</v>
       </c>
-      <c r="I205">
+      <c r="I205" s="5">
         <v>2</v>
       </c>
       <c r="J205">
@@ -9677,10 +9689,10 @@
       <c r="G206">
         <v>0</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="5">
         <v>18</v>
       </c>
-      <c r="I206">
+      <c r="I206" s="5">
         <v>2</v>
       </c>
       <c r="J206">
@@ -9710,10 +9722,10 @@
       <c r="G207">
         <v>0</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I207">
+      <c r="I207" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J207">
@@ -9743,10 +9755,10 @@
       <c r="G208">
         <v>0</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="5">
         <v>72</v>
       </c>
-      <c r="I208">
+      <c r="I208" s="5">
         <v>2</v>
       </c>
       <c r="J208">
@@ -9776,10 +9788,10 @@
       <c r="G209">
         <v>0</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="5">
         <v>15</v>
       </c>
-      <c r="I209">
+      <c r="I209" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J209">
@@ -9809,10 +9821,10 @@
       <c r="G210">
         <v>0</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="5">
         <v>12</v>
       </c>
-      <c r="I210">
+      <c r="I210" s="5">
         <v>2</v>
       </c>
       <c r="J210">
@@ -9842,10 +9854,10 @@
       <c r="G211">
         <v>0</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="5">
         <v>84</v>
       </c>
-      <c r="I211">
+      <c r="I211" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J211">
@@ -9881,10 +9893,10 @@
       <c r="G212">
         <v>0</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="5">
         <v>18</v>
       </c>
-      <c r="I212">
+      <c r="I212" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J212">
@@ -9914,10 +9926,10 @@
       <c r="G213">
         <v>0</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="5">
         <v>3.2183908045976999</v>
       </c>
-      <c r="I213">
+      <c r="I213" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J213">
@@ -9947,10 +9959,10 @@
       <c r="G214">
         <v>0</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="5">
         <v>18</v>
       </c>
-      <c r="I214">
+      <c r="I214" s="5">
         <v>1.3793103448275901</v>
       </c>
       <c r="J214">
